--- a/tabular/genus/erythro-refseqs-side-data.xlsx
+++ b/tabular/genus/erythro-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10814"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10308"/>
   <workbookPr date1904="1" showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB4328A6-4739-A342-969D-78199E759536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175E3DAD-559A-A042-A6DB-48C29C71F5B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18380" yWindow="2760" windowWidth="28800" windowHeight="17540" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REFSET" sheetId="3" r:id="rId1"/>
@@ -218,24 +218,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF660066"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1166,11 +1154,11 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="915">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2089,7 +2077,144 @@
     <cellStyle name="Hyperlink" xfId="913" builtinId="8" hidden="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <mruColors>
@@ -2107,6 +2232,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3442AE35-249C-4C4F-8F3D-341D48FF9759}" name="Table1" displayName="Table1" ref="A1:M10" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:M10" xr:uid="{8C613BBF-5BA6-954D-86B2-CBB54431A740}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{7532E4F1-12D9-EE4D-9BA5-37D14335CD29}" name="sequenceID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{5B265739-C460-6747-8100-6732CDB7F446}" name="virus_name" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{5391A9EC-5943-0F4E-9162-099144DE8C8E}" name="virus_full_name" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{841ECEED-C279-2647-ABBE-F76D8FAB8050}" name="host_species" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{4F8DC57B-9199-264B-B337-F92E9829C0BA}" name="assign_clade" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{E1C1EB68-E51B-9142-A98C-1947F9C623AB}" name="virus_subfamily" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{64283176-C1E1-434C-A741-D85783C378E4}" name="virus_genus" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{DAE8E43F-5F97-1741-8B66-52C831356C48}" name="assign_subclade" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{7B1DAA1A-46A3-4243-A662-88BAA2367354}" name="virus_clade_ns" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{6AB50F81-EB51-4D47-A38A-9E8FCEB60FC1}" name="virus_subclade_ns" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{AB26BBFB-3993-844D-8936-6F4E86A3A1DE}" name="virus_clade_vp" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{AA0108B1-F8BD-4A41-87C6-6333B9EFD6BE}" name="virus_subclade_vp" dataDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{6A2205BE-5DD5-E04A-B357-9DAB19B93AAD}" name="lab_construct" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2440,7 +2587,7 @@
     <col min="4" max="8" width="18.6640625" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
     <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="11" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
     <col min="12" max="12" width="19.5" customWidth="1"/>
     <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
@@ -2861,6 +3008,9 @@
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{64002731-A6B0-56B0-2670-7721B7C09600}">
       <mx:PLV Mode="0" OnePage="0" WScale="0"/>
